--- a/spend-analysis/outputs/EXHIBIT_B_CPO_PRESENTATION.xlsx
+++ b/spend-analysis/outputs/EXHIBIT_B_CPO_PRESENTATION.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -280,6 +280,8 @@
     <xf numFmtId="0" fontId="22" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1089,10 +1091,8 @@
           <t>Total 5-Year Exhibit B Spend:</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>$297,964,917.35</t>
-        </is>
+      <c r="C12" s="52" t="n">
+        <v>297964917.35</v>
       </c>
     </row>
     <row r="13">
@@ -1101,10 +1101,8 @@
           <t>Total Transaction Count:</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>5,103</t>
-        </is>
+      <c r="C13" s="53" t="n">
+        <v>5103</v>
       </c>
     </row>
     <row r="14">
@@ -1113,10 +1111,8 @@
           <t>Number of Departments Using Exhibit B:</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="C14" s="53" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -1125,10 +1121,8 @@
           <t>Number of Unique Vendors:</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
+      <c r="C15" s="53" t="n">
+        <v>589</v>
       </c>
     </row>
     <row r="16">
@@ -2080,7 +2074,6 @@
       <c r="G4" s="12" t="n">
         <v>0.05649167539429747</v>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2108,7 +2101,6 @@
       <c r="G5" s="12" t="n">
         <v>0.05479596341421479</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2136,7 +2128,6 @@
       <c r="G6" s="12" t="n">
         <v>0.05095252684398634</v>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2164,7 +2155,6 @@
       <c r="G7" s="12" t="n">
         <v>0.04801251841016833</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2192,7 +2182,6 @@
       <c r="G8" s="12" t="n">
         <v>0.02789969464810724</v>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2220,7 +2209,6 @@
       <c r="G9" s="12" t="n">
         <v>0.02607655934471093</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2248,7 +2236,6 @@
       <c r="G10" s="12" t="n">
         <v>0.01706172332353982</v>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2308,7 +2295,6 @@
       <c r="G12" s="12" t="n">
         <v>0.01606007103960225</v>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2336,7 +2322,6 @@
       <c r="G13" s="12" t="n">
         <v>0.01552360120476404</v>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2396,7 +2381,6 @@
       <c r="G15" s="12" t="n">
         <v>0.01544870500490856</v>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2424,7 +2408,6 @@
       <c r="G16" s="12" t="n">
         <v>0.0149075797897916</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,7 +2435,6 @@
       <c r="G17" s="12" t="n">
         <v>0.01449167448422456</v>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2512,7 +2494,6 @@
       <c r="G19" s="12" t="n">
         <v>0.01440788008916022</v>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2572,7 +2553,6 @@
       <c r="G21" s="12" t="n">
         <v>0.01298670707402239</v>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2600,7 +2580,6 @@
       <c r="G22" s="12" t="n">
         <v>0.0128740323997747</v>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2628,7 +2607,6 @@
       <c r="G23" s="12" t="n">
         <v>0.01287050540737125</v>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2656,7 +2634,6 @@
       <c r="G24" s="12" t="n">
         <v>0.01258364938834968</v>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2684,7 +2661,6 @@
       <c r="G25" s="12" t="n">
         <v>0.01241988809580068</v>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2712,7 +2688,6 @@
       <c r="G26" s="12" t="n">
         <v>0.01211933241026716</v>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2836,7 +2811,6 @@
       <c r="G30" s="12" t="n">
         <v>0.00849987264439825</v>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2864,7 +2838,6 @@
       <c r="G31" s="12" t="n">
         <v>0.008408063681641797</v>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2892,7 +2865,6 @@
       <c r="G32" s="12" t="n">
         <v>0.008165762773731745</v>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2920,7 +2892,6 @@
       <c r="G33" s="12" t="n">
         <v>0.008116298292708516</v>
       </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3012,7 +2983,6 @@
       <c r="G36" s="12" t="n">
         <v>0.007294770704244407</v>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3040,7 +3010,6 @@
       <c r="G37" s="12" t="n">
         <v>0.007219118039493655</v>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3068,7 +3037,6 @@
       <c r="G38" s="12" t="n">
         <v>0.007018539056803637</v>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3096,7 +3064,6 @@
       <c r="G39" s="12" t="n">
         <v>0.006900000638543664</v>
       </c>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3124,7 +3091,6 @@
       <c r="G40" s="12" t="n">
         <v>0.006848552601854721</v>
       </c>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3152,7 +3118,6 @@
       <c r="G41" s="12" t="n">
         <v>0.006658865069167705</v>
       </c>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3180,7 +3145,6 @@
       <c r="G42" s="12" t="n">
         <v>0.006554966025364125</v>
       </c>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3208,7 +3172,6 @@
       <c r="G43" s="12" t="n">
         <v>0.006283061430958501</v>
       </c>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3236,7 +3199,6 @@
       <c r="G44" s="12" t="n">
         <v>0.006158159109132818</v>
       </c>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3264,7 +3226,6 @@
       <c r="G45" s="12" t="n">
         <v>0.006125421899374528</v>
       </c>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3292,7 +3253,6 @@
       <c r="G46" s="12" t="n">
         <v>0.005901580949934961</v>
       </c>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3320,7 +3280,6 @@
       <c r="G47" s="12" t="n">
         <v>0.005732416101778465</v>
       </c>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3348,7 +3307,6 @@
       <c r="G48" s="12" t="n">
         <v>0.005675121739235208</v>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3376,7 +3334,6 @@
       <c r="G49" s="12" t="n">
         <v>0.005621894734724454</v>
       </c>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3404,7 +3361,6 @@
       <c r="G50" s="12" t="n">
         <v>0.005455991310794114</v>
       </c>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3464,7 +3420,6 @@
       <c r="G52" s="12" t="n">
         <v>0.004789003392332269</v>
       </c>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3492,7 +3447,6 @@
       <c r="G53" s="12" t="n">
         <v>0.004731973188404393</v>
       </c>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3520,7 +3474,6 @@
       <c r="G54" s="12" t="n">
         <v>0.004586093464086077</v>
       </c>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3548,7 +3501,6 @@
       <c r="G55" s="12" t="n">
         <v>0.004346894297173622</v>
       </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3576,7 +3528,6 @@
       <c r="G56" s="12" t="n">
         <v>0.004286013505699426</v>
       </c>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3604,7 +3555,6 @@
       <c r="G57" s="12" t="n">
         <v>0.004251671945991999</v>
       </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3632,7 +3582,6 @@
       <c r="G58" s="12" t="n">
         <v>0.004135116277933789</v>
       </c>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3660,7 +3609,6 @@
       <c r="G59" s="12" t="n">
         <v>0.003875248637515435</v>
       </c>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3720,7 +3668,6 @@
       <c r="G61" s="12" t="n">
         <v>0.003736906377741438</v>
       </c>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3748,7 +3695,6 @@
       <c r="G62" s="12" t="n">
         <v>0.003545380340022131</v>
       </c>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3776,7 +3722,6 @@
       <c r="G63" s="12" t="n">
         <v>0.003539415040429852</v>
       </c>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3900,7 +3845,6 @@
       <c r="G67" s="12" t="n">
         <v>0.003283879218708363</v>
       </c>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3928,7 +3872,6 @@
       <c r="G68" s="12" t="n">
         <v>0.003272259360804431</v>
       </c>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3956,7 +3899,6 @@
       <c r="G69" s="12" t="n">
         <v>0.003247869341789581</v>
       </c>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3984,7 +3926,6 @@
       <c r="G70" s="12" t="n">
         <v>0.003231407269530963</v>
       </c>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4012,7 +3953,6 @@
       <c r="G71" s="12" t="n">
         <v>0.003189845430271462</v>
       </c>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4040,7 +3980,6 @@
       <c r="G72" s="12" t="n">
         <v>0.003138447970006529</v>
       </c>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4068,7 +4007,6 @@
       <c r="G73" s="12" t="n">
         <v>0.003061136854977838</v>
       </c>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4096,7 +4034,6 @@
       <c r="G74" s="12" t="n">
         <v>0.003045150140695113</v>
       </c>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4124,7 +4061,6 @@
       <c r="G75" s="12" t="n">
         <v>0.002978679530074436</v>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4152,7 +4088,6 @@
       <c r="G76" s="12" t="n">
         <v>0.002945610267801779</v>
       </c>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4180,7 +4115,6 @@
       <c r="G77" s="12" t="n">
         <v>0.002943293484986768</v>
       </c>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4208,7 +4142,6 @@
       <c r="G78" s="12" t="n">
         <v>0.002867953004639556</v>
       </c>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4236,7 +4169,6 @@
       <c r="G79" s="12" t="n">
         <v>0.002777068143963463</v>
       </c>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4264,7 +4196,6 @@
       <c r="G80" s="12" t="n">
         <v>0.002768805828984003</v>
       </c>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4292,7 +4223,6 @@
       <c r="G81" s="12" t="n">
         <v>0.002745978074426779</v>
       </c>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4320,7 +4250,6 @@
       <c r="G82" s="12" t="n">
         <v>0.002721063329207957</v>
       </c>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4348,7 +4277,6 @@
       <c r="G83" s="12" t="n">
         <v>0.002720181379741105</v>
       </c>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4376,7 +4304,6 @@
       <c r="G84" s="12" t="n">
         <v>0.002611589367341014</v>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4404,7 +4331,6 @@
       <c r="G85" s="12" t="n">
         <v>0.002541079321438184</v>
       </c>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4432,7 +4358,6 @@
       <c r="G86" s="12" t="n">
         <v>0.002511745364683664</v>
       </c>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4460,7 +4385,6 @@
       <c r="G87" s="12" t="n">
         <v>0.002506994872536555</v>
       </c>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4488,7 +4412,6 @@
       <c r="G88" s="12" t="n">
         <v>0.002494392650659708</v>
       </c>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4516,7 +4439,6 @@
       <c r="G89" s="12" t="n">
         <v>0.002456180165441164</v>
       </c>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4544,7 +4466,6 @@
       <c r="G90" s="12" t="n">
         <v>0.00244681322377302</v>
       </c>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4572,7 +4493,6 @@
       <c r="G91" s="12" t="n">
         <v>0.002443717221706083</v>
       </c>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4600,7 +4520,6 @@
       <c r="G92" s="12" t="n">
         <v>0.002415049417201174</v>
       </c>
-      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4628,7 +4547,6 @@
       <c r="G93" s="12" t="n">
         <v>0.002362462857215551</v>
       </c>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4656,7 +4574,6 @@
       <c r="G94" s="12" t="n">
         <v>0.002333164844289905</v>
       </c>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4684,7 +4601,6 @@
       <c r="G95" s="12" t="n">
         <v>0.002323407420409849</v>
       </c>
-      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4712,7 +4628,6 @@
       <c r="G96" s="12" t="n">
         <v>0.002289210441481873</v>
       </c>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4740,7 +4655,6 @@
       <c r="G97" s="12" t="n">
         <v>0.002256374562389417</v>
       </c>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4800,7 +4714,6 @@
       <c r="G99" s="12" t="n">
         <v>0.002215025869028314</v>
       </c>
-      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4828,7 +4741,6 @@
       <c r="G100" s="12" t="n">
         <v>0.002203478502880095</v>
       </c>
-      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4856,7 +4768,6 @@
       <c r="G101" s="12" t="n">
         <v>0.002181464871012733</v>
       </c>
-      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4884,7 +4795,6 @@
       <c r="G102" s="12" t="n">
         <v>0.002142336673963334</v>
       </c>
-      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4976,7 +4886,6 @@
       <c r="G105" s="12" t="n">
         <v>0.002081479677236732</v>
       </c>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5004,7 +4913,6 @@
       <c r="G106" s="12" t="n">
         <v>0.002063924191018866</v>
       </c>
-      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5032,7 +4940,6 @@
       <c r="G107" s="12" t="n">
         <v>0.002055544006458275</v>
       </c>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5060,7 +4967,6 @@
       <c r="G108" s="12" t="n">
         <v>0.002047247190772855</v>
       </c>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5088,7 +4994,6 @@
       <c r="G109" s="12" t="n">
         <v>0.002013659880934831</v>
       </c>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5116,7 +5021,6 @@
       <c r="G110" s="12" t="n">
         <v>0.001996444834124735</v>
       </c>
-      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5144,7 +5048,6 @@
       <c r="G111" s="12" t="n">
         <v>0.001966224833461605</v>
       </c>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5172,7 +5075,6 @@
       <c r="G112" s="12" t="n">
         <v>0.001809306964017961</v>
       </c>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5200,7 +5102,6 @@
       <c r="G113" s="12" t="n">
         <v>0.001772809378676017</v>
       </c>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5228,7 +5129,6 @@
       <c r="G114" s="12" t="n">
         <v>0.001726678612268671</v>
       </c>
-      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5256,7 +5156,6 @@
       <c r="G115" s="12" t="n">
         <v>0.001720025245095076</v>
       </c>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5316,7 +5215,6 @@
       <c r="G117" s="12" t="n">
         <v>0.001693622170297257</v>
       </c>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5344,7 +5242,6 @@
       <c r="G118" s="12" t="n">
         <v>0.001693466245900477</v>
       </c>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5372,7 +5269,6 @@
       <c r="G119" s="12" t="n">
         <v>0.001682276505747112</v>
       </c>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5400,7 +5296,6 @@
       <c r="G120" s="12" t="n">
         <v>0.001666253209976549</v>
       </c>
-      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5428,7 +5323,6 @@
       <c r="G121" s="12" t="n">
         <v>0.001660195449834737</v>
       </c>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5488,7 +5382,6 @@
       <c r="G123" s="12" t="n">
         <v>0.001634821422358071</v>
       </c>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5516,7 +5409,6 @@
       <c r="G124" s="12" t="n">
         <v>0.001618208359169381</v>
       </c>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5544,7 +5436,6 @@
       <c r="G125" s="12" t="n">
         <v>0.001588554868152754</v>
       </c>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5572,7 +5463,6 @@
       <c r="G126" s="12" t="n">
         <v>0.001575772759326544</v>
       </c>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5600,7 +5490,6 @@
       <c r="G127" s="12" t="n">
         <v>0.001553243261358685</v>
       </c>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5628,7 +5517,6 @@
       <c r="G128" s="12" t="n">
         <v>0.001541570410638886</v>
       </c>
-      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5656,7 +5544,6 @@
       <c r="G129" s="12" t="n">
         <v>0.001498813665606038</v>
       </c>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5684,7 +5571,6 @@
       <c r="G130" s="12" t="n">
         <v>0.001468082228894149</v>
       </c>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5712,7 +5598,6 @@
       <c r="G131" s="12" t="n">
         <v>0.001455218298354777</v>
       </c>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5740,7 +5625,6 @@
       <c r="G132" s="12" t="n">
         <v>0.001418621708068687</v>
       </c>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5768,7 +5652,6 @@
       <c r="G133" s="12" t="n">
         <v>0.001412701078164767</v>
       </c>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5796,7 +5679,6 @@
       <c r="G134" s="12" t="n">
         <v>0.001361894559952892</v>
       </c>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5856,7 +5738,6 @@
       <c r="G136" s="12" t="n">
         <v>0.001349717958652879</v>
       </c>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5884,7 +5765,6 @@
       <c r="G137" s="12" t="n">
         <v>0.00134239595571582</v>
       </c>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5912,7 +5792,6 @@
       <c r="G138" s="12" t="n">
         <v>0.001297132573302187</v>
       </c>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5940,7 +5819,6 @@
       <c r="G139" s="12" t="n">
         <v>0.001292950872949445</v>
       </c>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -5968,7 +5846,6 @@
       <c r="G140" s="12" t="n">
         <v>0.001283083268312904</v>
       </c>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5996,7 +5873,6 @@
       <c r="G141" s="12" t="n">
         <v>0.001273266777076341</v>
       </c>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6024,7 +5900,6 @@
       <c r="G142" s="12" t="n">
         <v>0.001272697649671993</v>
       </c>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6052,7 +5927,6 @@
       <c r="G143" s="12" t="n">
         <v>0.001264006592942884</v>
       </c>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6080,7 +5954,6 @@
       <c r="G144" s="12" t="n">
         <v>0.001260376971007499</v>
       </c>
-      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6108,7 +5981,6 @@
       <c r="G145" s="12" t="n">
         <v>0.001256720936566676</v>
       </c>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6136,7 +6008,6 @@
       <c r="G146" s="12" t="n">
         <v>0.001228897996625811</v>
       </c>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6164,7 +6035,6 @@
       <c r="G147" s="12" t="n">
         <v>0.001187355555623164</v>
       </c>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6192,7 +6062,6 @@
       <c r="G148" s="12" t="n">
         <v>0.001178256531402177</v>
       </c>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6220,7 +6089,6 @@
       <c r="G149" s="12" t="n">
         <v>0.001178108493839931</v>
       </c>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6248,7 +6116,6 @@
       <c r="G150" s="12" t="n">
         <v>0.001173212447644427</v>
       </c>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6276,7 +6143,6 @@
       <c r="G151" s="12" t="n">
         <v>0.001172184910568184</v>
       </c>
-      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6304,7 +6170,6 @@
       <c r="G152" s="12" t="n">
         <v>0.001150915695197806</v>
       </c>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -6332,7 +6197,6 @@
       <c r="G153" s="12" t="n">
         <v>0.001145767505224212</v>
       </c>
-      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6360,7 +6224,6 @@
       <c r="G154" s="12" t="n">
         <v>0.001136273468056583</v>
       </c>
-      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6388,7 +6251,6 @@
       <c r="G155" s="12" t="n">
         <v>0.001110366022077457</v>
       </c>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -6416,7 +6278,6 @@
       <c r="G156" s="12" t="n">
         <v>0.0011098900600036</v>
       </c>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6444,7 +6305,6 @@
       <c r="G157" s="12" t="n">
         <v>0.001092208616004082</v>
       </c>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6472,7 +6332,6 @@
       <c r="G158" s="12" t="n">
         <v>0.001089755810464113</v>
       </c>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -6500,7 +6359,6 @@
       <c r="G159" s="12" t="n">
         <v>0.001057171437490786</v>
       </c>
-      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6528,7 +6386,6 @@
       <c r="G160" s="12" t="n">
         <v>0.001020071667161449</v>
       </c>
-      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6556,7 +6413,6 @@
       <c r="G161" s="12" t="n">
         <v>0.001009497905565662</v>
       </c>
-      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6584,7 +6440,6 @@
       <c r="G162" s="12" t="n">
         <v>0.0009946733750832177</v>
       </c>
-      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6612,7 +6467,6 @@
       <c r="G163" s="12" t="n">
         <v>0.0009872535418369429</v>
       </c>
-      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6640,7 +6494,6 @@
       <c r="G164" s="12" t="n">
         <v>0.000981424264969621</v>
       </c>
-      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6668,7 +6521,6 @@
       <c r="G165" s="12" t="n">
         <v>0.0009630671373970546</v>
       </c>
-      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6696,7 +6548,6 @@
       <c r="G166" s="12" t="n">
         <v>0.0009606835681959921</v>
       </c>
-      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6724,7 +6575,6 @@
       <c r="G167" s="12" t="n">
         <v>0.0009426167096952627</v>
       </c>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6752,7 +6602,6 @@
       <c r="G168" s="12" t="n">
         <v>0.0009393704550402096</v>
       </c>
-      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6812,7 +6661,6 @@
       <c r="G170" s="12" t="n">
         <v>0.0008705230545400695</v>
       </c>
-      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -6840,7 +6688,6 @@
       <c r="G171" s="12" t="n">
         <v>0.0008613765750678894</v>
       </c>
-      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -6868,7 +6715,6 @@
       <c r="G172" s="12" t="n">
         <v>0.0008558658591937311</v>
       </c>
-      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -6896,7 +6742,6 @@
       <c r="G173" s="12" t="n">
         <v>0.0008390249503895128</v>
       </c>
-      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -6924,7 +6769,6 @@
       <c r="G174" s="12" t="n">
         <v>0.0008345371737348693</v>
       </c>
-      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -6984,7 +6828,6 @@
       <c r="G176" s="12" t="n">
         <v>0.0008184446751863984</v>
       </c>
-      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -7012,7 +6855,6 @@
       <c r="G177" s="12" t="n">
         <v>0.0007902004104764463</v>
       </c>
-      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -7040,7 +6882,6 @@
       <c r="G178" s="12" t="n">
         <v>0.0007863006225070358</v>
       </c>
-      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -7068,7 +6909,6 @@
       <c r="G179" s="12" t="n">
         <v>0.0007761649326183462</v>
       </c>
-      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -7096,7 +6936,6 @@
       <c r="G180" s="12" t="n">
         <v>0.0007458111108317295</v>
       </c>
-      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -7124,7 +6963,6 @@
       <c r="G181" s="12" t="n">
         <v>0.0007405653724613034</v>
       </c>
-      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -7152,7 +6990,6 @@
       <c r="G182" s="12" t="n">
         <v>0.0007365847024866754</v>
       </c>
-      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -7180,7 +7017,6 @@
       <c r="G183" s="12" t="n">
         <v>0.0007260230564111722</v>
       </c>
-      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -7240,7 +7076,6 @@
       <c r="G185" s="12" t="n">
         <v>0.000707792923655097</v>
       </c>
-      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -7268,7 +7103,6 @@
       <c r="G186" s="12" t="n">
         <v>0.0006935531264410783</v>
       </c>
-      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -7296,7 +7130,6 @@
       <c r="G187" s="12" t="n">
         <v>0.0006896980752820227</v>
       </c>
-      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -7324,7 +7157,6 @@
       <c r="G188" s="12" t="n">
         <v>0.0006848670367396758</v>
       </c>
-      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -7352,7 +7184,6 @@
       <c r="G189" s="12" t="n">
         <v>0.0006803256296102035</v>
       </c>
-      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -7380,7 +7211,6 @@
       <c r="G190" s="12" t="n">
         <v>0.0006761628240993449</v>
       </c>
-      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -7440,7 +7270,6 @@
       <c r="G192" s="12" t="n">
         <v>0.0006413756414602672</v>
       </c>
-      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -7468,7 +7297,6 @@
       <c r="G193" s="12" t="n">
         <v>0.0005873174652726589</v>
       </c>
-      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -7496,7 +7324,6 @@
       <c r="G194" s="12" t="n">
         <v>0.0005832346020590736</v>
       </c>
-      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -7524,7 +7351,6 @@
       <c r="G195" s="12" t="n">
         <v>0.0005643027423954905</v>
       </c>
-      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -7552,7 +7378,6 @@
       <c r="G196" s="12" t="n">
         <v>0.0005593443734266725</v>
       </c>
-      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -7580,7 +7405,6 @@
       <c r="G197" s="12" t="n">
         <v>0.0005486451272593055</v>
       </c>
-      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -7640,7 +7464,6 @@
       <c r="G199" s="12" t="n">
         <v>0.0005131833349991166</v>
       </c>
-      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -7668,7 +7491,6 @@
       <c r="G200" s="12" t="n">
         <v>0.0005022973889997888</v>
       </c>
-      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -7696,7 +7518,6 @@
       <c r="G201" s="12" t="n">
         <v>0.0005003893120186111</v>
       </c>
-      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -7724,7 +7545,6 @@
       <c r="G202" s="12" t="n">
         <v>0.0004993557339627252</v>
       </c>
-      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -7784,7 +7604,6 @@
       <c r="G204" s="12" t="n">
         <v>0.0004816586169771334</v>
       </c>
-      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -7812,7 +7631,6 @@
       <c r="G205" s="12" t="n">
         <v>0.0004746397705351489</v>
       </c>
-      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -7840,7 +7658,6 @@
       <c r="G206" s="12" t="n">
         <v>0.0004693824401960082</v>
       </c>
-      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -7868,7 +7685,6 @@
       <c r="G207" s="12" t="n">
         <v>0.0004575834672456667</v>
       </c>
-      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -7896,7 +7712,6 @@
       <c r="G208" s="12" t="n">
         <v>0.0004529204350593858</v>
       </c>
-      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -7924,7 +7739,6 @@
       <c r="G209" s="12" t="n">
         <v>0.0004501469541833783</v>
       </c>
-      <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -7984,7 +7798,6 @@
       <c r="G211" s="12" t="n">
         <v>0.0004341674555152259</v>
       </c>
-      <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -8012,7 +7825,6 @@
       <c r="G212" s="12" t="n">
         <v>0.00042580579998164</v>
       </c>
-      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -8040,7 +7852,6 @@
       <c r="G213" s="12" t="n">
         <v>0.0004198916137893384</v>
       </c>
-      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -8068,7 +7879,6 @@
       <c r="G214" s="12" t="n">
         <v>0.0004195544264422758</v>
       </c>
-      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -8096,7 +7906,6 @@
       <c r="G215" s="12" t="n">
         <v>0.0004161563753931983</v>
       </c>
-      <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -8124,7 +7933,6 @@
       <c r="G216" s="12" t="n">
         <v>0.0004156898775207817</v>
       </c>
-      <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -8152,7 +7960,6 @@
       <c r="G217" s="12" t="n">
         <v>0.0004094441757900822</v>
       </c>
-      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -8180,7 +7987,6 @@
       <c r="G218" s="12" t="n">
         <v>0.0004093508762155989</v>
       </c>
-      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -8240,7 +8046,6 @@
       <c r="G220" s="12" t="n">
         <v>0.0003958768738542997</v>
       </c>
-      <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -8268,7 +8073,6 @@
       <c r="G221" s="12" t="n">
         <v>0.000391623285843809</v>
       </c>
-      <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -8328,7 +8132,6 @@
       <c r="G223" s="12" t="n">
         <v>0.0003842885968494999</v>
       </c>
-      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -8356,7 +8159,6 @@
       <c r="G224" s="12" t="n">
         <v>0.0003523904791635954</v>
       </c>
-      <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -8384,7 +8186,6 @@
       <c r="G225" s="12" t="n">
         <v>0.0003518772643819411</v>
       </c>
-      <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -8444,7 +8245,6 @@
       <c r="G227" s="12" t="n">
         <v>0.0003466919223835438</v>
       </c>
-      <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -8472,7 +8272,6 @@
       <c r="G228" s="12" t="n">
         <v>0.0003455308125351988</v>
       </c>
-      <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -8500,7 +8299,6 @@
       <c r="G229" s="12" t="n">
         <v>0.0003427512571185504</v>
       </c>
-      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -8528,7 +8326,6 @@
       <c r="G230" s="12" t="n">
         <v>0.0003367080960108749</v>
       </c>
-      <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -8556,7 +8353,6 @@
       <c r="G231" s="12" t="n">
         <v>0.0003356099801558051</v>
       </c>
-      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -8584,7 +8380,6 @@
       <c r="G232" s="12" t="n">
         <v>0.0003346828575856247</v>
       </c>
-      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -8612,7 +8407,6 @@
       <c r="G233" s="12" t="n">
         <v>0.0003244374567944223</v>
       </c>
-      <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -8640,7 +8434,6 @@
       <c r="G234" s="12" t="n">
         <v>0.0003174165631315589</v>
       </c>
-      <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -8668,7 +8461,6 @@
       <c r="G235" s="12" t="n">
         <v>0.0003105499829375712</v>
       </c>
-      <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -8696,7 +8488,6 @@
       <c r="G236" s="12" t="n">
         <v>0.0003012068360170197</v>
       </c>
-      <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -8724,7 +8515,6 @@
       <c r="G237" s="12" t="n">
         <v>0.0003003709322394456</v>
       </c>
-      <c r="H237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -8752,7 +8542,6 @@
       <c r="G238" s="12" t="n">
         <v>0.0002957648530667972</v>
       </c>
-      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -8780,7 +8569,6 @@
       <c r="G239" s="12" t="n">
         <v>0.0002936670893248353</v>
       </c>
-      <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -8808,7 +8596,6 @@
       <c r="G240" s="12" t="n">
         <v>0.0002924066389223642</v>
       </c>
-      <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -8836,7 +8623,6 @@
       <c r="G241" s="12" t="n">
         <v>0.0002910850739425066</v>
       </c>
-      <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -8864,7 +8650,6 @@
       <c r="G242" s="12" t="n">
         <v>0.0002898905037791401</v>
       </c>
-      <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -8892,7 +8677,6 @@
       <c r="G243" s="12" t="n">
         <v>0.0002891999526839715</v>
       </c>
-      <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -8920,7 +8704,6 @@
       <c r="G244" s="12" t="n">
         <v>0.0002839501400083863</v>
       </c>
-      <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -8948,7 +8731,6 @@
       <c r="G245" s="12" t="n">
         <v>0.0002827983936784876</v>
       </c>
-      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -8976,7 +8758,6 @@
       <c r="G246" s="12" t="n">
         <v>0.0002819123833308763</v>
       </c>
-      <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -9004,7 +8785,6 @@
       <c r="G247" s="12" t="n">
         <v>0.0002798287487690789</v>
       </c>
-      <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -9032,7 +8812,6 @@
       <c r="G248" s="12" t="n">
         <v>0.0002797680704846668</v>
       </c>
-      <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -9060,7 +8839,6 @@
       <c r="G249" s="12" t="n">
         <v>0.0002794085650739239</v>
       </c>
-      <c r="H249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -9088,7 +8866,6 @@
       <c r="G250" s="12" t="n">
         <v>0.0002723265232726761</v>
       </c>
-      <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -9116,7 +8893,6 @@
       <c r="G251" s="12" t="n">
         <v>0.0002660438708831614</v>
       </c>
-      <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -9144,7 +8920,6 @@
       <c r="G252" s="12" t="n">
         <v>0.0002550635849184119</v>
       </c>
-      <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -9172,7 +8947,6 @@
       <c r="G253" s="12" t="n">
         <v>0.0002416710686602945</v>
       </c>
-      <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -9200,7 +8974,6 @@
       <c r="G254" s="12" t="n">
         <v>0.0002395080623381903</v>
       </c>
-      <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -9228,7 +9001,6 @@
       <c r="G255" s="12" t="n">
         <v>0.0002357660110594531</v>
       </c>
-      <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -9256,7 +9028,6 @@
       <c r="G256" s="12" t="n">
         <v>0.0002349269861090636</v>
       </c>
-      <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -9284,7 +9055,6 @@
       <c r="G257" s="12" t="n">
         <v>0.0002349269861090636</v>
       </c>
-      <c r="H257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -9312,7 +9082,6 @@
       <c r="G258" s="12" t="n">
         <v>0.0002345913761289078</v>
       </c>
-      <c r="H258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -9340,7 +9109,6 @@
       <c r="G259" s="12" t="n">
         <v>0.0002334553363460804</v>
       </c>
-      <c r="H259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -9368,7 +9136,6 @@
       <c r="G260" s="12" t="n">
         <v>0.0002312017153293341</v>
       </c>
-      <c r="H260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -9396,7 +9163,6 @@
       <c r="G261" s="12" t="n">
         <v>0.0002295404459275629</v>
       </c>
-      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -9424,7 +9190,6 @@
       <c r="G262" s="12" t="n">
         <v>0.0002279005548815276</v>
       </c>
-      <c r="H262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -9452,7 +9217,6 @@
       <c r="G263" s="12" t="n">
         <v>0.0002272079565654801</v>
       </c>
-      <c r="H263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -9480,7 +9244,6 @@
       <c r="G264" s="12" t="n">
         <v>0.000225314445057441</v>
       </c>
-      <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -9508,7 +9271,6 @@
       <c r="G265" s="12" t="n">
         <v>0.0002226772218333767</v>
       </c>
-      <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -9536,7 +9298,6 @@
       <c r="G266" s="12" t="n">
         <v>0.0002189855120516628</v>
       </c>
-      <c r="H266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -9564,7 +9325,6 @@
       <c r="G267" s="12" t="n">
         <v>0.0002165017632715238</v>
       </c>
-      <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -9592,7 +9352,6 @@
       <c r="G268" s="12" t="n">
         <v>0.0002152884325102665</v>
       </c>
-      <c r="H268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -9620,7 +9379,6 @@
       <c r="G269" s="12" t="n">
         <v>0.0002134479473790921</v>
       </c>
-      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -9648,7 +9406,6 @@
       <c r="G270" s="12" t="n">
         <v>0.0002113503850031183</v>
       </c>
-      <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -9676,7 +9433,6 @@
       <c r="G271" s="12" t="n">
         <v>0.0002083785586288386</v>
       </c>
-      <c r="H271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -9704,7 +9460,6 @@
       <c r="G272" s="12" t="n">
         <v>0.0002053933078553527</v>
       </c>
-      <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -9732,7 +9487,6 @@
       <c r="G273" s="12" t="n">
         <v>0.0001967222199200632</v>
       </c>
-      <c r="H273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -9760,7 +9514,6 @@
       <c r="G274" s="12" t="n">
         <v>0.0001956645115066042</v>
       </c>
-      <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -9788,7 +9541,6 @@
       <c r="G275" s="12" t="n">
         <v>0.0001953207462039306</v>
       </c>
-      <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -9816,7 +9568,6 @@
       <c r="G276" s="12" t="n">
         <v>0.0001905734423516327</v>
       </c>
-      <c r="H276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -9844,7 +9595,6 @@
       <c r="G277" s="12" t="n">
         <v>0.0001873275568675578</v>
       </c>
-      <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -9872,7 +9622,6 @@
       <c r="G278" s="12" t="n">
         <v>0.0001872140871332671</v>
       </c>
-      <c r="H278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -9900,7 +9649,6 @@
       <c r="G279" s="12" t="n">
         <v>0.0001870564175645899</v>
       </c>
-      <c r="H279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -9928,7 +9676,6 @@
       <c r="G280" s="12" t="n">
         <v>0.0001845421618372547</v>
       </c>
-      <c r="H280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -9956,7 +9703,6 @@
       <c r="G281" s="12" t="n">
         <v>0.0001829074391849138</v>
       </c>
-      <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -9984,7 +9730,6 @@
       <c r="G282" s="12" t="n">
         <v>0.0001824375852126957</v>
       </c>
-      <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -10012,7 +9757,6 @@
       <c r="G283" s="12" t="n">
         <v>0.0001772386174491041</v>
       </c>
-      <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -10040,7 +9784,6 @@
       <c r="G284" s="12" t="n">
         <v>0.0001742976336320007</v>
       </c>
-      <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -10068,7 +9811,6 @@
       <c r="G285" s="12" t="n">
         <v>0.000172342437009609</v>
       </c>
-      <c r="H285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -10096,7 +9838,6 @@
       <c r="G286" s="12" t="n">
         <v>0.000166328306165217</v>
       </c>
-      <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -10124,7 +9865,6 @@
       <c r="G287" s="12" t="n">
         <v>0.0001661269401771235</v>
       </c>
-      <c r="H287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -10152,7 +9892,6 @@
       <c r="G288" s="12" t="n">
         <v>0.0001645609504487185</v>
       </c>
-      <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -10180,7 +9919,6 @@
       <c r="G289" s="12" t="n">
         <v>0.0001615559658083995</v>
       </c>
-      <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -10208,7 +9946,6 @@
       <c r="G290" s="12" t="n">
         <v>0.0001610927904747865</v>
       </c>
-      <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -10236,7 +9973,6 @@
       <c r="G291" s="12" t="n">
         <v>0.0001572302552131733</v>
       </c>
-      <c r="H291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -10264,7 +10000,6 @@
       <c r="G292" s="12" t="n">
         <v>0.0001560821334710603</v>
       </c>
-      <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -10292,7 +10027,6 @@
       <c r="G293" s="12" t="n">
         <v>0.0001537362197097712</v>
       </c>
-      <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -10320,7 +10054,6 @@
       <c r="G294" s="12" t="n">
         <v>0.0001527025409708913</v>
       </c>
-      <c r="H294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -10348,7 +10081,6 @@
       <c r="G295" s="12" t="n">
         <v>0.0001518336131712699</v>
       </c>
-      <c r="H295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -10376,7 +10108,6 @@
       <c r="G296" s="12" t="n">
         <v>0.0001513601010502681</v>
       </c>
-      <c r="H296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -10404,7 +10135,6 @@
       <c r="G297" s="12" t="n">
         <v>0.0001476683912685543</v>
       </c>
-      <c r="H297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -10432,7 +10162,6 @@
       <c r="G298" s="12" t="n">
         <v>0.0001476100622540032</v>
       </c>
-      <c r="H298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -10460,7 +10189,6 @@
       <c r="G299" s="12" t="n">
         <v>0.0001452166932415201</v>
       </c>
-      <c r="H299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -10520,7 +10248,6 @@
       <c r="G301" s="12" t="n">
         <v>0.0001409561916654382</v>
       </c>
-      <c r="H301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -10548,7 +10275,6 @@
       <c r="G302" s="12" t="n">
         <v>0.0001409561916654382</v>
       </c>
-      <c r="H302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -10576,7 +10302,6 @@
       <c r="G303" s="12" t="n">
         <v>0.0001404555622580397</v>
       </c>
-      <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -10604,7 +10329,6 @@
       <c r="G304" s="12" t="n">
         <v>0.0001356048905318538</v>
       </c>
-      <c r="H304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -10632,7 +10356,6 @@
       <c r="G305" s="12" t="n">
         <v>0.0001352122268550715</v>
       </c>
-      <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -10692,7 +10415,6 @@
       <c r="G307" s="12" t="n">
         <v>0.0001333210646168936</v>
       </c>
-      <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -10720,7 +10442,6 @@
       <c r="G308" s="12" t="n">
         <v>0.0001310892582488575</v>
       </c>
-      <c r="H308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -10780,7 +10501,6 @@
       <c r="G310" s="12" t="n">
         <v>0.0001296125743361719</v>
       </c>
-      <c r="H310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -10808,7 +10528,6 @@
       <c r="G311" s="12" t="n">
         <v>0.0001290572069410101</v>
       </c>
-      <c r="H311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -10836,7 +10555,6 @@
       <c r="G312" s="12" t="n">
         <v>0.0001284886165126301</v>
       </c>
-      <c r="H312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -10864,7 +10582,6 @@
       <c r="G313" s="12" t="n">
         <v>0.0001284406242854679</v>
       </c>
-      <c r="H313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -10892,7 +10609,6 @@
       <c r="G314" s="12" t="n">
         <v>0.0001282207661874678</v>
       </c>
-      <c r="H314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -10920,7 +10636,6 @@
       <c r="G315" s="12" t="n">
         <v>0.0001270070998162304</v>
       </c>
-      <c r="H315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -10948,7 +10663,6 @@
       <c r="G316" s="12" t="n">
         <v>0.0001260967241840597</v>
       </c>
-      <c r="H316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -10976,7 +10690,6 @@
       <c r="G317" s="12" t="n">
         <v>0.0001252116199833948</v>
       </c>
-      <c r="H317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -11004,7 +10717,6 @@
       <c r="G318" s="12" t="n">
         <v>0.0001248528193536102</v>
       </c>
-      <c r="H318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -11032,7 +10744,6 @@
       <c r="G319" s="12" t="n">
         <v>0.0001223264816669894</v>
       </c>
-      <c r="H319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -11060,7 +10771,6 @@
       <c r="G320" s="12" t="n">
         <v>0.0001205041194747434</v>
       </c>
-      <c r="H320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -11088,7 +10798,6 @@
       <c r="G321" s="12" t="n">
         <v>0.0001189066159692018</v>
       </c>
-      <c r="H321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -11116,7 +10825,6 @@
       <c r="G322" s="12" t="n">
         <v>0.0001184703229949992</v>
       </c>
-      <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -11144,7 +10852,6 @@
       <c r="G323" s="12" t="n">
         <v>0.0001174634930545318</v>
       </c>
-      <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -11172,7 +10879,6 @@
       <c r="G324" s="12" t="n">
         <v>0.0001149136962302981</v>
       </c>
-      <c r="H324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -11200,7 +10906,6 @@
       <c r="G325" s="12" t="n">
         <v>0.0001112859537108019</v>
       </c>
-      <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -11228,7 +10933,6 @@
       <c r="G326" s="12" t="n">
         <v>0.0001089054385605588</v>
       </c>
-      <c r="H326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -11256,7 +10960,6 @@
       <c r="G327" s="12" t="n">
         <v>0.0001087451847950344</v>
       </c>
-      <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -11284,7 +10987,6 @@
       <c r="G328" s="12" t="n">
         <v>0.0001077681905818028</v>
       </c>
-      <c r="H328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -11312,7 +11014,6 @@
       <c r="G329" s="12" t="n">
         <v>0.000105280750091882</v>
       </c>
-      <c r="H329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -11340,7 +11041,6 @@
       <c r="G330" s="12" t="n">
         <v>0.000103701805818243</v>
       </c>
-      <c r="H330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -11368,7 +11068,6 @@
       <c r="G331" s="12" t="n">
         <v>0.000102781932423634</v>
       </c>
-      <c r="H331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -11396,7 +11095,6 @@
       <c r="G332" s="12" t="n">
         <v>0.000100391013364006</v>
       </c>
-      <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -11424,7 +11122,6 @@
       <c r="G333" s="12" t="n">
         <v>9.970301290468659e-05</v>
       </c>
-      <c r="H333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -11452,7 +11149,6 @@
       <c r="G334" s="12" t="n">
         <v>9.665567428487188e-05</v>
       </c>
-      <c r="H334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -11480,7 +11176,6 @@
       <c r="G335" s="12" t="n">
         <v>9.434721459736818e-05</v>
       </c>
-      <c r="H335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -11508,7 +11203,6 @@
       <c r="G336" s="12" t="n">
         <v>9.372784637899065e-05</v>
       </c>
-      <c r="H336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -11536,7 +11230,6 @@
       <c r="G337" s="12" t="n">
         <v>9.316435722230904e-05</v>
       </c>
-      <c r="H337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -11564,7 +11257,6 @@
       <c r="G338" s="12" t="n">
         <v>9.286932248875408e-05</v>
       </c>
-      <c r="H338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -11592,7 +11284,6 @@
       <c r="G339" s="12" t="n">
         <v>9.26283545230022e-05</v>
       </c>
-      <c r="H339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -11620,7 +11311,6 @@
       <c r="G340" s="12" t="n">
         <v>9.202321616778328e-05</v>
       </c>
-      <c r="H340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -11648,7 +11338,6 @@
       <c r="G341" s="12" t="n">
         <v>9.061469464206737e-05</v>
       </c>
-      <c r="H341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -11676,7 +11365,6 @@
       <c r="G342" s="12" t="n">
         <v>8.893664474128836e-05</v>
       </c>
-      <c r="H342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -11704,7 +11392,6 @@
       <c r="G343" s="12" t="n">
         <v>8.830969173735929e-05</v>
       </c>
-      <c r="H343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -11732,7 +11419,6 @@
       <c r="G344" s="12" t="n">
         <v>8.812379736935099e-05</v>
       </c>
-      <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -11760,7 +11446,6 @@
       <c r="G345" s="12" t="n">
         <v>8.769693503559082e-05</v>
       </c>
-      <c r="H345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -11788,7 +11473,6 @@
       <c r="G346" s="12" t="n">
         <v>8.544361606782673e-05</v>
       </c>
-      <c r="H346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -11816,7 +11500,6 @@
       <c r="G347" s="12" t="n">
         <v>8.507712996949659e-05</v>
       </c>
-      <c r="H347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -11844,7 +11527,6 @@
       <c r="G348" s="12" t="n">
         <v>8.451078812798367e-05</v>
       </c>
-      <c r="H348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -11872,7 +11554,6 @@
       <c r="G349" s="12" t="n">
         <v>8.390249503895128e-05</v>
       </c>
-      <c r="H349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -11900,7 +11581,6 @@
       <c r="G350" s="12" t="n">
         <v>8.168894585383565e-05</v>
       </c>
-      <c r="H350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -11928,7 +11608,6 @@
       <c r="G351" s="12" t="n">
         <v>8.159349837547934e-05</v>
       </c>
-      <c r="H351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -11956,7 +11635,6 @@
       <c r="G352" s="12" t="n">
         <v>8.054639523739323e-05</v>
       </c>
-      <c r="H352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -11984,7 +11662,6 @@
       <c r="G353" s="12" t="n">
         <v>7.971824405036076e-05</v>
       </c>
-      <c r="H353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -12012,7 +11689,6 @@
       <c r="G354" s="12" t="n">
         <v>7.769505284598951e-05</v>
       </c>
-      <c r="H354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -12040,7 +11716,6 @@
       <c r="G355" s="12" t="n">
         <v>7.463892124469471e-05</v>
       </c>
-      <c r="H355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -12068,7 +11743,6 @@
       <c r="G356" s="12" t="n">
         <v>7.451481267403309e-05</v>
       </c>
-      <c r="H356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -12096,7 +11770,6 @@
       <c r="G357" s="12" t="n">
         <v>7.436949355262563e-05</v>
       </c>
-      <c r="H357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -12124,7 +11797,6 @@
       <c r="G358" s="12" t="n">
         <v>7.391809812931608e-05</v>
       </c>
-      <c r="H358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -12152,7 +11824,6 @@
       <c r="G359" s="12" t="n">
         <v>7.328188228993472e-05</v>
       </c>
-      <c r="H359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -12180,7 +11851,6 @@
       <c r="G360" s="12" t="n">
         <v>7.302584543607385e-05</v>
       </c>
-      <c r="H360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -12208,7 +11878,6 @@
       <c r="G361" s="12" t="n">
         <v>7.282736569380971e-05</v>
       </c>
-      <c r="H361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -12236,7 +11905,6 @@
       <c r="G362" s="12" t="n">
         <v>7.181758238551692e-05</v>
       </c>
-      <c r="H362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -12264,7 +11932,6 @@
       <c r="G363" s="12" t="n">
         <v>7.160574536604257e-05</v>
       </c>
-      <c r="H363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -12292,7 +11959,6 @@
       <c r="G364" s="12" t="n">
         <v>7.080699361327176e-05</v>
       </c>
-      <c r="H364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -12320,7 +11986,6 @@
       <c r="G365" s="12" t="n">
         <v>6.903497291804911e-05</v>
       </c>
-      <c r="H365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -12348,7 +12013,6 @@
       <c r="G366" s="12" t="n">
         <v>6.846406678080606e-05</v>
       </c>
-      <c r="H366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -12376,7 +12040,6 @@
       <c r="G367" s="12" t="n">
         <v>6.784637661232931e-05</v>
       </c>
-      <c r="H367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -12404,7 +12067,6 @@
       <c r="G368" s="12" t="n">
         <v>6.488448429346226e-05</v>
       </c>
-      <c r="H368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -12432,7 +12094,6 @@
       <c r="G369" s="12" t="n">
         <v>6.21549683248551e-05</v>
       </c>
-      <c r="H369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -12460,7 +12121,6 @@
       <c r="G370" s="12" t="n">
         <v>6.212979757634342e-05</v>
       </c>
-      <c r="H370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -12488,7 +12148,6 @@
       <c r="G371" s="12" t="n">
         <v>6.086286990125526e-05</v>
       </c>
-      <c r="H371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -12516,7 +12175,6 @@
       <c r="G372" s="12" t="n">
         <v>5.921166879888869e-05</v>
       </c>
-      <c r="H372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -12544,7 +12202,6 @@
       <c r="G373" s="12" t="n">
         <v>5.802364303013516e-05</v>
       </c>
-      <c r="H373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -12572,7 +12229,6 @@
       <c r="G374" s="12" t="n">
         <v>5.724163821537412e-05</v>
       </c>
-      <c r="H374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -12600,7 +12256,6 @@
       <c r="G375" s="12" t="n">
         <v>5.684394038888949e-05</v>
       </c>
-      <c r="H375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -12628,7 +12283,6 @@
       <c r="G376" s="12" t="n">
         <v>5.663166707644094e-05</v>
       </c>
-      <c r="H376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -12656,7 +12310,6 @@
       <c r="G377" s="12" t="n">
         <v>5.396242666026976e-05</v>
       </c>
-      <c r="H377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -12684,7 +12337,6 @@
       <c r="G378" s="12" t="n">
         <v>5.344186202005009e-05</v>
       </c>
-      <c r="H378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -12712,7 +12364,6 @@
       <c r="G379" s="12" t="n">
         <v>5.084222711376323e-05</v>
       </c>
-      <c r="H379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -12740,7 +12391,6 @@
       <c r="G380" s="12" t="n">
         <v>5.080631684588656e-05</v>
       </c>
-      <c r="H380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -12768,7 +12418,6 @@
       <c r="G381" s="12" t="n">
         <v>5.005082521955782e-05</v>
       </c>
-      <c r="H381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -12796,7 +12445,6 @@
       <c r="G382" s="12" t="n">
         <v>4.821419960315518e-05</v>
       </c>
-      <c r="H382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -12824,7 +12472,6 @@
       <c r="G383" s="12" t="n">
         <v>4.777736965298438e-05</v>
       </c>
-      <c r="H383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -12852,7 +12499,6 @@
       <c r="G384" s="12" t="n">
         <v>4.724522646844934e-05</v>
       </c>
-      <c r="H384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -12880,7 +12526,6 @@
       <c r="G385" s="12" t="n">
         <v>4.705372741377244e-05</v>
       </c>
-      <c r="H385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -12908,7 +12553,6 @@
       <c r="G386" s="12" t="n">
         <v>4.464589361114461e-05</v>
       </c>
-      <c r="H386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -12936,7 +12580,6 @@
       <c r="G387" s="12" t="n">
         <v>4.454349900619908e-05</v>
       </c>
-      <c r="H387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -12964,7 +12607,6 @@
       <c r="G388" s="12" t="n">
         <v>4.423067694369585e-05</v>
       </c>
-      <c r="H388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -12992,7 +12634,6 @@
       <c r="G389" s="12" t="n">
         <v>4.413519590434153e-05</v>
       </c>
-      <c r="H389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -13020,7 +12661,6 @@
       <c r="G390" s="12" t="n">
         <v>4.384073170775282e-05</v>
       </c>
-      <c r="H390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -13048,7 +12688,6 @@
       <c r="G391" s="12" t="n">
         <v>4.343212655691313e-05</v>
       </c>
-      <c r="H391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -13076,7 +12715,6 @@
       <c r="G392" s="12" t="n">
         <v>4.33273826821065e-05</v>
       </c>
-      <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -13104,7 +12742,6 @@
       <c r="G393" s="12" t="n">
         <v>4.255198938395453e-05</v>
       </c>
-      <c r="H393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -13132,7 +12769,6 @@
       <c r="G394" s="12" t="n">
         <v>4.160013235823663e-05</v>
       </c>
-      <c r="H394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -13160,7 +12796,6 @@
       <c r="G395" s="12" t="n">
         <v>4.134714955519519e-05</v>
       </c>
-      <c r="H395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -13188,7 +12823,6 @@
       <c r="G396" s="12" t="n">
         <v>4.102496397424561e-05</v>
       </c>
-      <c r="H396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -13216,7 +12850,6 @@
       <c r="G397" s="12" t="n">
         <v>4.070284551529208e-05</v>
       </c>
-      <c r="H397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -13244,7 +12877,6 @@
       <c r="G398" s="12" t="n">
         <v>4.038730501194959e-05</v>
       </c>
-      <c r="H398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -13272,7 +12904,6 @@
       <c r="G399" s="12" t="n">
         <v>4.021446587216934e-05</v>
       </c>
-      <c r="H399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -13300,7 +12931,6 @@
       <c r="G400" s="12" t="n">
         <v>3.897495753245991e-05</v>
       </c>
-      <c r="H400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -13360,7 +12990,6 @@
       <c r="G402" s="12" t="n">
         <v>3.809945177722746e-05</v>
       </c>
-      <c r="H402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -13388,7 +13017,6 @@
       <c r="G403" s="12" t="n">
         <v>3.77057812705047e-05</v>
       </c>
-      <c r="H403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -13416,7 +13044,6 @@
       <c r="G404" s="12" t="n">
         <v>3.758831777745017e-05</v>
       </c>
-      <c r="H404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -13444,7 +13071,6 @@
       <c r="G405" s="12" t="n">
         <v>3.746615574467346e-05</v>
       </c>
-      <c r="H405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -13472,7 +13098,6 @@
       <c r="G406" s="12" t="n">
         <v>3.72753950319529e-05</v>
       </c>
-      <c r="H406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -13500,7 +13125,6 @@
       <c r="G407" s="12" t="n">
         <v>3.686675632011519e-05</v>
       </c>
-      <c r="H407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -13528,7 +13152,6 @@
       <c r="G408" s="12" t="n">
         <v>3.6767247960999e-05</v>
       </c>
-      <c r="H408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -13556,7 +13179,6 @@
       <c r="G409" s="12" t="n">
         <v>3.656554636292535e-05</v>
       </c>
-      <c r="H409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -13584,7 +13206,6 @@
       <c r="G410" s="12" t="n">
         <v>3.54337017048499e-05</v>
       </c>
-      <c r="H410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -13612,7 +13233,6 @@
       <c r="G411" s="12" t="n">
         <v>3.53699358086203e-05</v>
       </c>
-      <c r="H411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -13640,7 +13260,6 @@
       <c r="G412" s="12" t="n">
         <v>3.521354155786769e-05</v>
       </c>
-      <c r="H412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -13668,7 +13287,6 @@
       <c r="G413" s="12" t="n">
         <v>3.470633419485823e-05</v>
       </c>
-      <c r="H413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -13696,7 +13314,6 @@
       <c r="G414" s="12" t="n">
         <v>3.423893017549524e-05</v>
       </c>
-      <c r="H414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -13724,7 +13341,6 @@
       <c r="G415" s="12" t="n">
         <v>3.417580193822793e-05</v>
       </c>
-      <c r="H415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -13752,7 +13368,6 @@
       <c r="G416" s="12" t="n">
         <v>3.403085198779863e-05</v>
       </c>
-      <c r="H416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -13780,7 +13395,6 @@
       <c r="G417" s="12" t="n">
         <v>3.384626649871294e-05</v>
       </c>
-      <c r="H417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -13808,7 +13422,6 @@
       <c r="G418" s="12" t="n">
         <v>3.356099801558051e-05</v>
       </c>
-      <c r="H418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -13836,7 +13449,6 @@
       <c r="G419" s="12" t="n">
         <v>3.021781919825846e-05</v>
       </c>
-      <c r="H419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -13864,7 +13476,6 @@
       <c r="G420" s="12" t="n">
         <v>2.962590387625766e-05</v>
       </c>
-      <c r="H420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -13892,7 +13503,6 @@
       <c r="G421" s="12" t="n">
         <v>2.923834147117374e-05</v>
       </c>
-      <c r="H421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -13920,7 +13530,6 @@
       <c r="G422" s="12" t="n">
         <v>2.889783158530767e-05</v>
       </c>
-      <c r="H422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -13948,7 +13557,6 @@
       <c r="G423" s="12" t="n">
         <v>2.792654274173874e-05</v>
       </c>
-      <c r="H423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -13976,7 +13584,6 @@
       <c r="G424" s="12" t="n">
         <v>2.735298528565247e-05</v>
       </c>
-      <c r="H424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -14004,7 +13611,6 @@
       <c r="G425" s="12" t="n">
         <v>2.721142499602276e-05</v>
       </c>
-      <c r="H425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -14032,7 +13638,6 @@
       <c r="G426" s="12" t="n">
         <v>2.682678239776619e-05</v>
       </c>
-      <c r="H426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -14060,7 +13665,6 @@
       <c r="G427" s="12" t="n">
         <v>2.606011495909827e-05</v>
       </c>
-      <c r="H427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -14088,7 +13692,6 @@
       <c r="G428" s="12" t="n">
         <v>2.571040935977592e-05</v>
       </c>
-      <c r="H428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -14116,7 +13719,6 @@
       <c r="G429" s="12" t="n">
         <v>2.569973696240696e-05</v>
       </c>
-      <c r="H429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -14144,7 +13746,6 @@
       <c r="G430" s="12" t="n">
         <v>2.540856174362379e-05</v>
       </c>
-      <c r="H430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -14172,7 +13773,6 @@
       <c r="G431" s="12" t="n">
         <v>2.535221282795562e-05</v>
       </c>
-      <c r="H431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -14200,7 +13800,6 @@
       <c r="G432" s="12" t="n">
         <v>2.513634848871941e-05</v>
       </c>
-      <c r="H432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -14228,7 +13827,6 @@
       <c r="G433" s="12" t="n">
         <v>2.490226052756074e-05</v>
       </c>
-      <c r="H433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -14256,7 +13854,6 @@
       <c r="G434" s="12" t="n">
         <v>2.466766915143183e-05</v>
       </c>
-      <c r="H434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -14284,7 +13881,6 @@
       <c r="G435" s="12" t="n">
         <v>2.466733354145168e-05</v>
       </c>
-      <c r="H435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -14312,7 +13908,6 @@
       <c r="G436" s="12" t="n">
         <v>2.449952855137377e-05</v>
       </c>
-      <c r="H436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -14340,7 +13935,6 @@
       <c r="G437" s="12" t="n">
         <v>2.420754786863822e-05</v>
       </c>
-      <c r="H437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -14368,7 +13962,6 @@
       <c r="G438" s="12" t="n">
         <v>2.420043293705892e-05</v>
       </c>
-      <c r="H438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -14396,7 +13989,6 @@
       <c r="G439" s="12" t="n">
         <v>2.415888442151563e-05</v>
       </c>
-      <c r="H439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -14424,7 +14016,6 @@
       <c r="G440" s="12" t="n">
         <v>2.282147865059475e-05</v>
       </c>
-      <c r="H440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -14452,7 +14043,6 @@
       <c r="G441" s="12" t="n">
         <v>2.25357403134901e-05</v>
       </c>
-      <c r="H441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -14480,7 +14070,6 @@
       <c r="G442" s="12" t="n">
         <v>2.231806368036104e-05</v>
       </c>
-      <c r="H442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -14508,7 +14097,6 @@
       <c r="G443" s="12" t="n">
         <v>2.212005379206911e-05</v>
       </c>
-      <c r="H443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -14536,7 +14124,6 @@
       <c r="G444" s="12" t="n">
         <v>2.198570911701275e-05</v>
       </c>
-      <c r="H444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -14564,7 +14151,6 @@
       <c r="G445" s="12" t="n">
         <v>2.174752671409617e-05</v>
       </c>
-      <c r="H445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -14592,7 +14178,6 @@
       <c r="G446" s="12" t="n">
         <v>2.168543886776735e-05</v>
       </c>
-      <c r="H446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -14620,7 +14205,6 @@
       <c r="G447" s="12" t="n">
         <v>2.116356534862507e-05</v>
       </c>
-      <c r="H447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -14648,7 +14232,6 @@
       <c r="G448" s="12" t="n">
         <v>2.013659880934831e-05</v>
       </c>
-      <c r="H448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -14676,7 +14259,6 @@
       <c r="G449" s="12" t="n">
         <v>2.013659880934831e-05</v>
       </c>
-      <c r="H449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -14704,7 +14286,6 @@
       <c r="G450" s="12" t="n">
         <v>1.986116369863444e-05</v>
       </c>
-      <c r="H450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -14732,7 +14313,6 @@
       <c r="G451" s="12" t="n">
         <v>1.979763272939094e-05</v>
       </c>
-      <c r="H451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -14760,7 +14340,6 @@
       <c r="G452" s="12" t="n">
         <v>1.89538085562852e-05</v>
       </c>
-      <c r="H452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -14788,7 +14367,6 @@
       <c r="G453" s="12" t="n">
         <v>1.877875439063593e-05</v>
       </c>
-      <c r="H453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -14816,7 +14394,6 @@
       <c r="G454" s="12" t="n">
         <v>1.829074391849138e-05</v>
       </c>
-      <c r="H454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -14844,7 +14421,6 @@
       <c r="G455" s="12" t="n">
         <v>1.812293892841348e-05</v>
       </c>
-      <c r="H455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -14872,7 +14448,6 @@
       <c r="G456" s="12" t="n">
         <v>1.786055904592767e-05</v>
       </c>
-      <c r="H456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -14900,7 +14475,6 @@
       <c r="G457" s="12" t="n">
         <v>1.785445094428883e-05</v>
       </c>
-      <c r="H457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -14928,7 +14502,6 @@
       <c r="G458" s="12" t="n">
         <v>1.75607922116525e-05</v>
       </c>
-      <c r="H458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -14956,7 +14529,6 @@
       <c r="G459" s="12" t="n">
         <v>1.741349299136212e-05</v>
       </c>
-      <c r="H459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -14984,7 +14556,6 @@
       <c r="G460" s="12" t="n">
         <v>1.701139867413745e-05</v>
       </c>
-      <c r="H460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -15012,7 +14583,6 @@
       <c r="G461" s="12" t="n">
         <v>1.678049900779025e-05</v>
       </c>
-      <c r="H461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -15040,7 +14610,6 @@
       <c r="G462" s="12" t="n">
         <v>1.661094884581554e-05</v>
       </c>
-      <c r="H462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -15068,7 +14637,6 @@
       <c r="G463" s="12" t="n">
         <v>1.529065918388261e-05</v>
       </c>
-      <c r="H463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -15096,7 +14664,6 @@
       <c r="G464" s="12" t="n">
         <v>1.495142461594112e-05</v>
       </c>
-      <c r="H464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -15124,7 +14691,6 @@
       <c r="G465" s="12" t="n">
         <v>1.493128801713177e-05</v>
       </c>
-      <c r="H465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -15152,7 +14718,6 @@
       <c r="G466" s="12" t="n">
         <v>1.480308500471225e-05</v>
       </c>
-      <c r="H466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -15212,7 +14777,6 @@
       <c r="G468" s="12" t="n">
         <v>1.456490260179568e-05</v>
       </c>
-      <c r="H468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -15240,7 +14804,6 @@
       <c r="G469" s="12" t="n">
         <v>1.43969298067277e-05</v>
       </c>
-      <c r="H469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -15268,7 +14831,6 @@
       <c r="G470" s="12" t="n">
         <v>1.420301436019367e-05</v>
       </c>
-      <c r="H470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -15296,7 +14858,6 @@
       <c r="G471" s="12" t="n">
         <v>1.409561916654381e-05</v>
       </c>
-      <c r="H471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -15324,7 +14885,6 @@
       <c r="G472" s="12" t="n">
         <v>1.396902708202904e-05</v>
       </c>
-      <c r="H472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -15352,7 +14912,6 @@
       <c r="G473" s="12" t="n">
         <v>1.358549199670699e-05</v>
       </c>
-      <c r="H473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -15380,7 +14939,6 @@
       <c r="G474" s="12" t="n">
         <v>1.34243992062322e-05</v>
       </c>
-      <c r="H474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -15408,7 +14966,6 @@
       <c r="G475" s="12" t="n">
         <v>1.326602485659668e-05</v>
       </c>
-      <c r="H475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -15436,7 +14993,6 @@
       <c r="G476" s="12" t="n">
         <v>1.320960881893249e-05</v>
       </c>
-      <c r="H476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -15464,7 +15020,6 @@
       <c r="G477" s="12" t="n">
         <v>1.303844772905303e-05</v>
       </c>
-      <c r="H477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -15492,7 +15047,6 @@
       <c r="G478" s="12" t="n">
         <v>1.274109728663498e-05</v>
       </c>
-      <c r="H478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -15520,7 +15074,6 @@
       <c r="G479" s="12" t="n">
         <v>1.27363987469128e-05</v>
       </c>
-      <c r="H479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -15548,7 +15101,6 @@
       <c r="G480" s="12" t="n">
         <v>1.264038073159023e-05</v>
       </c>
-      <c r="H480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -15576,7 +15128,6 @@
       <c r="G481" s="12" t="n">
         <v>1.22911449862401e-05</v>
       </c>
-      <c r="H481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -15604,7 +15155,6 @@
       <c r="G482" s="12" t="n">
         <v>1.19090194628347e-05</v>
       </c>
-      <c r="H482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -15632,7 +15182,6 @@
       <c r="G483" s="12" t="n">
         <v>1.180743032184153e-05</v>
       </c>
-      <c r="H483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -15660,7 +15209,6 @@
       <c r="G484" s="12" t="n">
         <v>1.089772590963121e-05</v>
       </c>
-      <c r="H484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -15688,7 +15236,6 @@
       <c r="G485" s="12" t="n">
         <v>1.040390938482996e-05</v>
       </c>
-      <c r="H485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -15716,7 +15263,6 @@
       <c r="G486" s="12" t="n">
         <v>1.006829940467415e-05</v>
       </c>
-      <c r="H486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -15776,7 +15322,6 @@
       <c r="G488" s="12" t="n">
         <v>9.843574961961826e-06</v>
       </c>
-      <c r="H488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -15804,7 +15349,6 @@
       <c r="G489" s="12" t="n">
         <v>9.727252542839824e-06</v>
       </c>
-      <c r="H489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -15832,7 +15376,6 @@
       <c r="G490" s="12" t="n">
         <v>9.628985940650204e-06</v>
       </c>
-      <c r="H490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -15860,7 +15403,6 @@
       <c r="G491" s="12" t="n">
         <v>9.000791179794568e-06</v>
       </c>
-      <c r="H491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -15888,7 +15430,6 @@
       <c r="G492" s="12" t="n">
         <v>8.809761979089885e-06</v>
       </c>
-      <c r="H492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -15916,7 +15457,6 @@
       <c r="G493" s="12" t="n">
         <v>8.776200981074304e-06</v>
       </c>
-      <c r="H493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -15944,7 +15484,6 @@
       <c r="G494" s="12" t="n">
         <v>8.727671777943773e-06</v>
       </c>
-      <c r="H494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -15972,7 +15511,6 @@
       <c r="G495" s="12" t="n">
         <v>8.719147284447817e-06</v>
       </c>
-      <c r="H495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -16000,7 +15538,6 @@
       <c r="G496" s="12" t="n">
         <v>8.198515522232116e-06</v>
       </c>
-      <c r="H496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -16028,7 +15565,6 @@
       <c r="G497" s="12" t="n">
         <v>8.139716653708819e-06</v>
       </c>
-      <c r="H497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -16056,7 +15592,6 @@
       <c r="G498" s="12" t="n">
         <v>8.101624920961135e-06</v>
       </c>
-      <c r="H498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -16084,7 +15619,6 @@
       <c r="G499" s="12" t="n">
         <v>8.021078525723741e-06</v>
       </c>
-      <c r="H499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -16112,7 +15646,6 @@
       <c r="G500" s="12" t="n">
         <v>7.767189575735876e-06</v>
       </c>
-      <c r="H500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -16140,7 +15673,6 @@
       <c r="G501" s="12" t="n">
         <v>7.088082780890604e-06</v>
       </c>
-      <c r="H501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -16168,7 +15700,6 @@
       <c r="G502" s="12" t="n">
         <v>6.946824540243025e-06</v>
       </c>
-      <c r="H502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -16196,7 +15727,6 @@
       <c r="G503" s="12" t="n">
         <v>6.843087495376866e-06</v>
       </c>
-      <c r="H503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -16224,7 +15754,6 @@
       <c r="G504" s="12" t="n">
         <v>6.830434999124993e-06</v>
       </c>
-      <c r="H504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -16252,7 +15781,6 @@
       <c r="G505" s="12" t="n">
         <v>6.643735167164317e-06</v>
       </c>
-      <c r="H505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -16280,7 +15808,6 @@
       <c r="G506" s="12" t="n">
         <v>6.521438890395543e-06</v>
       </c>
-      <c r="H506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -16308,7 +15835,6 @@
       <c r="G507" s="12" t="n">
         <v>6.418675114471836e-06</v>
       </c>
-      <c r="H507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -16336,7 +15862,6 @@
       <c r="G508" s="12" t="n">
         <v>6.249057830501091e-06</v>
       </c>
-      <c r="H508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -16364,7 +15889,6 @@
       <c r="G509" s="12" t="n">
         <v>6.040979642804492e-06</v>
       </c>
-      <c r="H509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -16392,7 +15916,6 @@
       <c r="G510" s="12" t="n">
         <v>5.841694436587975e-06</v>
       </c>
-      <c r="H510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -16420,7 +15943,6 @@
       <c r="G511" s="12" t="n">
         <v>5.565017568947529e-06</v>
       </c>
-      <c r="H511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -16448,7 +15970,6 @@
       <c r="G512" s="12" t="n">
         <v>5.23551569043056e-06</v>
       </c>
-      <c r="H512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -16476,7 +15997,6 @@
       <c r="G513" s="12" t="n">
         <v>5.193363076922991e-06</v>
       </c>
-      <c r="H513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -16504,7 +16024,6 @@
       <c r="G514" s="12" t="n">
         <v>5.024383451914542e-06</v>
       </c>
-      <c r="H514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -16532,7 +16051,6 @@
       <c r="G515" s="12" t="n">
         <v>4.68511532297504e-06</v>
       </c>
-      <c r="H515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -16560,7 +16078,6 @@
       <c r="G516" s="12" t="n">
         <v>3.958016300967487e-06</v>
       </c>
-      <c r="H516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -16588,7 +16105,6 @@
       <c r="G517" s="12" t="n">
         <v>3.947578830584642e-06</v>
       </c>
-      <c r="H517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -16616,7 +16132,6 @@
       <c r="G518" s="12" t="n">
         <v>3.917709542350775e-06</v>
       </c>
-      <c r="H518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -16644,7 +16159,6 @@
       <c r="G519" s="12" t="n">
         <v>3.84773486148829e-06</v>
       </c>
-      <c r="H519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -16672,7 +16186,6 @@
       <c r="G520" s="12" t="n">
         <v>3.792392775760598e-06</v>
       </c>
-      <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -16700,7 +16213,6 @@
       <c r="G521" s="12" t="n">
         <v>3.359455901359609e-06</v>
       </c>
-      <c r="H521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -16728,7 +16240,6 @@
       <c r="G522" s="12" t="n">
         <v>3.356099801558051e-06</v>
       </c>
-      <c r="H522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -16756,7 +16267,6 @@
       <c r="G523" s="12" t="n">
         <v>3.356099801558051e-06</v>
       </c>
-      <c r="H523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -16784,7 +16294,6 @@
       <c r="G524" s="12" t="n">
         <v>3.302402204733122e-06</v>
       </c>
-      <c r="H524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -16812,7 +16321,6 @@
       <c r="G525" s="12" t="n">
         <v>3.241891725311031e-06</v>
       </c>
-      <c r="H525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -16840,7 +16348,6 @@
       <c r="G526" s="12" t="n">
         <v>3.128724040002493e-06</v>
       </c>
-      <c r="H526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -16900,7 +16407,6 @@
       <c r="G528" s="12" t="n">
         <v>2.953367825371085e-06</v>
       </c>
-      <c r="H528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -16928,7 +16434,6 @@
       <c r="G529" s="12" t="n">
         <v>2.90973852795083e-06</v>
       </c>
-      <c r="H529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -16956,7 +16461,6 @@
       <c r="G530" s="12" t="n">
         <v>2.899670228546156e-06</v>
       </c>
-      <c r="H530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -16984,7 +16488,6 @@
       <c r="G531" s="12" t="n">
         <v>2.858155274000883e-06</v>
       </c>
-      <c r="H531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -17012,7 +16515,6 @@
       <c r="G532" s="12" t="n">
         <v>2.73857743807137e-06</v>
       </c>
-      <c r="H532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -17040,7 +16542,6 @@
       <c r="G533" s="12" t="n">
         <v>2.700317900333608e-06</v>
       </c>
-      <c r="H533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -17068,7 +16569,6 @@
       <c r="G534" s="12" t="n">
         <v>2.550635849184119e-06</v>
       </c>
-      <c r="H534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -17096,7 +16596,6 @@
       <c r="G535" s="12" t="n">
         <v>2.376219342497147e-06</v>
       </c>
-      <c r="H535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -17124,7 +16623,6 @@
       <c r="G536" s="12" t="n">
         <v>2.312117836287388e-06</v>
       </c>
-      <c r="H536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -17152,7 +16650,6 @@
       <c r="G537" s="12" t="n">
         <v>2.235162467837662e-06</v>
       </c>
-      <c r="H537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -17180,7 +16677,6 @@
       <c r="G538" s="12" t="n">
         <v>2.103670477612618e-06</v>
       </c>
-      <c r="H538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -17208,7 +16704,6 @@
       <c r="G539" s="12" t="n">
         <v>2.020372080537947e-06</v>
       </c>
-      <c r="H539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -17236,7 +16731,6 @@
       <c r="G540" s="12" t="n">
         <v>2.01365988093483e-06</v>
       </c>
-      <c r="H540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -17264,7 +16758,6 @@
       <c r="G541" s="12" t="n">
         <v>2.006947681331714e-06</v>
       </c>
-      <c r="H541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -17292,7 +16785,6 @@
       <c r="G542" s="12" t="n">
         <v>1.922877381302685e-06</v>
       </c>
-      <c r="H542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -17320,7 +16812,6 @@
       <c r="G543" s="12" t="n">
         <v>1.896196387880299e-06</v>
       </c>
-      <c r="H543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -17348,7 +16839,6 @@
       <c r="G544" s="12" t="n">
         <v>1.761952395817977e-06</v>
       </c>
-      <c r="H544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -17376,7 +16866,6 @@
       <c r="G545" s="12" t="n">
         <v>1.639119143080952e-06</v>
       </c>
-      <c r="H545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -17404,7 +16893,6 @@
       <c r="G546" s="12" t="n">
         <v>1.510244910701123e-06</v>
       </c>
-      <c r="H546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -17432,7 +16920,6 @@
       <c r="G547" s="12" t="n">
         <v>1.402849717051265e-06</v>
       </c>
-      <c r="H547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -17460,7 +16947,6 @@
       <c r="G548" s="12" t="n">
         <v>1.34243992062322e-06</v>
       </c>
-      <c r="H548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -17488,7 +16974,6 @@
       <c r="G549" s="12" t="n">
         <v>1.327270349520178e-06</v>
       </c>
-      <c r="H549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -17516,7 +17001,6 @@
       <c r="G550" s="12" t="n">
         <v>1.084355845883406e-06</v>
       </c>
-      <c r="H550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -17544,7 +17028,6 @@
       <c r="G551" s="12" t="n">
         <v>1.006829940467415e-06</v>
       </c>
-      <c r="H551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -17572,7 +17055,6 @@
       <c r="G552" s="12" t="n">
         <v>9.413859943370334e-07</v>
       </c>
-      <c r="H552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -17600,7 +17082,6 @@
       <c r="G553" s="12" t="n">
         <v>9.061469464206738e-07</v>
       </c>
-      <c r="H553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -17628,7 +17109,6 @@
       <c r="G554" s="12" t="n">
         <v>8.390249503895128e-07</v>
       </c>
-      <c r="H554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -17656,7 +17136,6 @@
       <c r="G555" s="12" t="n">
         <v>7.848239385943502e-07</v>
       </c>
-      <c r="H555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -17684,7 +17163,6 @@
       <c r="G556" s="12" t="n">
         <v>5.671808664633106e-07</v>
       </c>
-      <c r="H556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -17712,7 +17190,6 @@
       <c r="G557" s="12" t="n">
         <v>5.492928545210061e-07</v>
       </c>
-      <c r="H557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -17740,7 +17217,6 @@
       <c r="G558" s="12" t="n">
         <v>4.147468134765439e-07</v>
       </c>
-      <c r="H558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -17768,7 +17244,6 @@
       <c r="G559" s="12" t="n">
         <v>3.504775022767073e-07</v>
       </c>
-      <c r="H559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -17796,7 +17271,6 @@
       <c r="G560" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -17824,7 +17298,6 @@
       <c r="G561" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -17852,7 +17325,6 @@
       <c r="G562" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -17880,7 +17352,6 @@
       <c r="G563" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -17908,7 +17379,6 @@
       <c r="G564" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -17936,7 +17406,6 @@
       <c r="G565" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -17964,7 +17433,6 @@
       <c r="G566" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -17992,7 +17460,6 @@
       <c r="G567" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -18020,7 +17487,6 @@
       <c r="G568" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -18048,7 +17514,6 @@
       <c r="G569" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -18076,7 +17541,6 @@
       <c r="G570" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -18104,7 +17568,6 @@
       <c r="G571" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -18132,7 +17595,6 @@
       <c r="G572" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -18160,7 +17622,6 @@
       <c r="G573" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -18188,7 +17649,6 @@
       <c r="G574" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -18216,7 +17676,6 @@
       <c r="G575" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -18244,7 +17703,6 @@
       <c r="G576" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -18272,7 +17730,6 @@
       <c r="G577" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -18300,7 +17757,6 @@
       <c r="G578" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -18328,7 +17784,6 @@
       <c r="G579" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -18356,7 +17811,6 @@
       <c r="G580" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -18384,7 +17838,6 @@
       <c r="G581" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -18412,7 +17865,6 @@
       <c r="G582" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -18440,7 +17892,6 @@
       <c r="G583" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -18468,7 +17919,6 @@
       <c r="G584" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -18496,7 +17946,6 @@
       <c r="G585" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -18524,7 +17973,6 @@
       <c r="G586" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -18552,7 +18000,6 @@
       <c r="G587" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -18580,7 +18027,6 @@
       <c r="G588" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -18608,7 +18054,6 @@
       <c r="G589" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -18636,7 +18081,6 @@
       <c r="G590" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -18664,7 +18108,6 @@
       <c r="G591" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -18692,7 +18135,6 @@
       <c r="G592" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H592" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
